--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779089</v>
+        <v>122779298</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1614,24 +1614,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506686</v>
+        <v>507119</v>
       </c>
       <c r="R9" t="n">
-        <v>7053093</v>
+        <v>7053255</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1665,7 +1661,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,11 +1676,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1722,7 +1713,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779188</v>
+        <v>122779089</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1774,10 +1765,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506664</v>
+        <v>506686</v>
       </c>
       <c r="R10" t="n">
-        <v>7053016</v>
+        <v>7053093</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1814,7 +1805,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1871,10 +1862,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779255</v>
+        <v>122779331</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1914,13 +1905,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506701</v>
+        <v>507003</v>
       </c>
       <c r="R11" t="n">
-        <v>7053096</v>
+        <v>7053201</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1950,6 +1941,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,12 +1960,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2007,10 +1998,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779331</v>
+        <v>122779254</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2023,26 +2014,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2050,13 +2045,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507003</v>
+        <v>506701</v>
       </c>
       <c r="R12" t="n">
-        <v>7053201</v>
+        <v>7053096</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2086,11 +2081,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2105,7 +2095,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2120,12 +2110,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2143,10 +2133,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779254</v>
+        <v>122779255</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2159,30 +2149,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2243,6 +2229,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2255,12 +2246,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,10 +2269,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779298</v>
+        <v>122779215</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2294,45 +2285,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507119</v>
+        <v>506627</v>
       </c>
       <c r="R14" t="n">
-        <v>7053255</v>
+        <v>7053057</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2364,17 +2350,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2395,12 +2377,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2421,7 +2403,7 @@
         <v>122779318</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2563,10 +2545,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122779215</v>
+        <v>122779188</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2579,37 +2561,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506627</v>
+        <v>506664</v>
       </c>
       <c r="R16" t="n">
-        <v>7053057</v>
+        <v>7053016</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2644,13 +2635,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2659,6 +2654,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779298</v>
+        <v>122779255</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,45 +1589,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507119</v>
+        <v>506701</v>
       </c>
       <c r="R9" t="n">
-        <v>7053255</v>
+        <v>7053096</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1659,17 +1654,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1678,6 +1669,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1690,12 +1686,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1862,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779331</v>
+        <v>122779298</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1878,37 +1874,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507003</v>
+        <v>507119</v>
       </c>
       <c r="R11" t="n">
-        <v>7053201</v>
+        <v>7053255</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1945,7 +1946,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,13 +1955,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779254</v>
+        <v>122779215</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2014,30 +2014,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2045,10 +2041,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R12" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2110,12 +2106,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2133,10 +2129,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2149,37 +2145,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R13" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2214,13 +2219,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2231,7 +2240,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2246,12 +2255,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2269,7 +2278,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779215</v>
+        <v>122779331</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2312,13 +2321,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506627</v>
+        <v>507003</v>
       </c>
       <c r="R14" t="n">
-        <v>7053057</v>
+        <v>7053201</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2348,6 +2357,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2362,7 +2376,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2545,10 +2559,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2561,46 +2575,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R16" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2635,17 +2644,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2654,11 +2659,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,37 +1589,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R9" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1654,13 +1663,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1671,7 +1684,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1686,12 +1699,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1722,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779089</v>
+        <v>122779298</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1725,16 +1738,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1750,24 +1763,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506686</v>
+        <v>507119</v>
       </c>
       <c r="R10" t="n">
-        <v>7053093</v>
+        <v>7053255</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1801,7 +1810,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,11 +1825,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1858,10 +1862,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779298</v>
+        <v>122779254</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1874,45 +1878,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507119</v>
+        <v>506701</v>
       </c>
       <c r="R11" t="n">
-        <v>7053255</v>
+        <v>7053096</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,17 +1947,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1975,12 +1974,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1998,10 +1997,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779215</v>
+        <v>122779318</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2014,26 +2013,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2041,10 +2044,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506627</v>
+        <v>507101</v>
       </c>
       <c r="R12" t="n">
-        <v>7053057</v>
+        <v>7053264</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2079,6 +2082,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2094,24 +2102,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2129,10 +2142,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779188</v>
+        <v>122779255</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2145,46 +2158,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R13" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2219,17 +2223,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779331</v>
+        <v>122779215</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507003</v>
+        <v>506627</v>
       </c>
       <c r="R14" t="n">
-        <v>7053201</v>
+        <v>7053057</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2357,11 +2357,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2376,7 +2371,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2414,10 +2409,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779318</v>
+        <v>122779089</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2430,41 +2425,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507101</v>
+        <v>506686</v>
       </c>
       <c r="R15" t="n">
-        <v>7053264</v>
+        <v>7053093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2510,7 +2510,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2521,27 +2520,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2559,10 +2558,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122779254</v>
+        <v>122779331</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2575,30 +2574,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2606,13 +2601,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506701</v>
+        <v>507003</v>
       </c>
       <c r="R16" t="n">
-        <v>7053096</v>
+        <v>7053201</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2642,6 +2637,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1722,10 +1722,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779298</v>
+        <v>122779254</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1738,45 +1738,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507119</v>
+        <v>506701</v>
       </c>
       <c r="R10" t="n">
-        <v>7053255</v>
+        <v>7053096</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,17 +1807,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1839,12 +1834,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779254</v>
+        <v>122779298</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1878,44 +1873,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506701</v>
+        <v>507119</v>
       </c>
       <c r="R11" t="n">
-        <v>7053096</v>
+        <v>7053255</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1947,13 +1943,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,46 +1589,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R9" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1663,17 +1658,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1682,11 +1673,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1699,12 +1685,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1722,10 +1708,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779254</v>
+        <v>122779331</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1738,30 +1724,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1769,13 +1751,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506701</v>
+        <v>507003</v>
       </c>
       <c r="R10" t="n">
-        <v>7053096</v>
+        <v>7053201</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1805,6 +1787,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1819,7 +1806,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1834,12 +1821,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1857,10 +1844,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779298</v>
+        <v>122779089</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1873,16 +1860,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1898,20 +1885,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507119</v>
+        <v>506686</v>
       </c>
       <c r="R11" t="n">
-        <v>7053255</v>
+        <v>7053093</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1945,7 +1936,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,6 +1951,11 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1997,10 +1993,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779318</v>
+        <v>122779188</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2013,41 +2009,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507101</v>
+        <v>506664</v>
       </c>
       <c r="R12" t="n">
-        <v>7053264</v>
+        <v>7053016</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2084,7 +2085,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,7 +2094,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2104,27 +2104,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779255</v>
+        <v>122779215</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506701</v>
+        <v>506627</v>
       </c>
       <c r="R13" t="n">
-        <v>7053096</v>
+        <v>7053057</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2236,11 +2236,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2278,10 +2273,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779215</v>
+        <v>122779298</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2294,40 +2289,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506627</v>
+        <v>507119</v>
       </c>
       <c r="R14" t="n">
-        <v>7053057</v>
+        <v>7053255</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2359,13 +2359,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2386,12 +2390,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2409,10 +2413,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779089</v>
+        <v>122779318</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2425,46 +2429,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506686</v>
+        <v>507101</v>
       </c>
       <c r="R15" t="n">
-        <v>7053093</v>
+        <v>7053264</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2501,7 +2500,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2510,6 +2509,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2520,27 +2520,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122779331</v>
+        <v>122779255</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507003</v>
+        <v>506701</v>
       </c>
       <c r="R16" t="n">
-        <v>7053201</v>
+        <v>7053096</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2637,11 +2637,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2656,7 +2651,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122768066</v>
+        <v>122779254</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,57 +1452,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506635</v>
+        <v>506701</v>
       </c>
       <c r="R8" t="n">
-        <v>7053059</v>
+        <v>7053096</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1534,17 +1521,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Synobservation av en hona som födosökte på en ca 20 meter hög stående död gran, både på stammen och en gren. Hörde även trummande av två spettar innan dess som antyder att det även kan finnas en hane av tretåig hackspett på/kring fyndplatsen. Dessutom rikligt med stående grov granved här (upp till 50 cm BHD) som indikerar mycket höga livsmiljövärden för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1553,9 +1536,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1573,10 +1571,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779254</v>
+        <v>122779331</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,30 +1587,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1620,13 +1614,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506701</v>
+        <v>507003</v>
       </c>
       <c r="R9" t="n">
-        <v>7053096</v>
+        <v>7053201</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1656,6 +1650,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,7 +1669,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1685,12 +1684,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1708,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779331</v>
+        <v>122779089</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1724,40 +1723,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507003</v>
+        <v>506686</v>
       </c>
       <c r="R10" t="n">
-        <v>7053201</v>
+        <v>7053093</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1791,7 +1799,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,13 +1808,17 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1821,12 +1833,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1844,7 +1856,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779089</v>
+        <v>122779188</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1896,10 +1908,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506686</v>
+        <v>506664</v>
       </c>
       <c r="R11" t="n">
-        <v>7053093</v>
+        <v>7053016</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1936,7 +1948,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1993,10 +2005,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2009,46 +2021,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R12" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2083,17 +2086,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2102,11 +2101,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2119,12 +2113,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2142,10 +2136,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779215</v>
+        <v>122779298</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,40 +2152,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506627</v>
+        <v>507119</v>
       </c>
       <c r="R13" t="n">
-        <v>7053057</v>
+        <v>7053255</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2223,13 +2222,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2250,12 +2253,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2273,10 +2276,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779298</v>
+        <v>122779318</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2289,45 +2292,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507119</v>
+        <v>507101</v>
       </c>
       <c r="R14" t="n">
-        <v>7053255</v>
+        <v>7053264</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2361,7 +2363,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,6 +2372,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2378,24 +2381,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2413,10 +2421,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779318</v>
+        <v>122779255</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2429,30 +2437,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2460,10 +2464,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507101</v>
+        <v>506701</v>
       </c>
       <c r="R15" t="n">
-        <v>7053264</v>
+        <v>7053096</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2498,11 +2502,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2525,22 +2524,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2558,14 +2557,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122779255</v>
+        <v>122768066</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2574,40 +2573,57 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506701</v>
+        <v>506635</v>
       </c>
       <c r="R16" t="n">
-        <v>7053096</v>
+        <v>7053059</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2639,13 +2655,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Synobservation av en hona som födosökte på en ca 20 meter hög stående död gran, både på stammen och en gren. Hörde även trummande av två spettar innan dess som antyder att det även kan finnas en hane av tretåig hackspett på/kring fyndplatsen. Dessutom rikligt med stående grov granved här (upp till 50 cm BHD) som indikerar mycket höga livsmiljövärden för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2656,27 +2676,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779254</v>
+        <v>122779318</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,28 +1452,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506701</v>
+        <v>507101</v>
       </c>
       <c r="R8" t="n">
-        <v>7053096</v>
+        <v>7053264</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1521,6 +1521,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1536,24 +1541,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1571,10 +1581,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779331</v>
+        <v>122779188</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,40 +1597,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507003</v>
+        <v>506664</v>
       </c>
       <c r="R9" t="n">
-        <v>7053201</v>
+        <v>7053016</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1673,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,13 +1682,17 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1684,12 +1707,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779089</v>
+        <v>122779255</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1723,46 +1746,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506686</v>
+        <v>506701</v>
       </c>
       <c r="R10" t="n">
-        <v>7053093</v>
+        <v>7053096</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1797,17 +1811,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1818,7 +1828,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1833,12 +1843,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1856,10 +1866,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,46 +1882,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R11" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1946,17 +1947,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1965,11 +1962,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1982,12 +1974,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2005,10 +1997,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779215</v>
+        <v>122779089</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2021,37 +2013,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506627</v>
+        <v>506686</v>
       </c>
       <c r="R12" t="n">
-        <v>7053057</v>
+        <v>7053093</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2086,13 +2087,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2101,6 +2106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2113,12 +2123,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2136,10 +2146,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779298</v>
+        <v>122779254</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2152,45 +2162,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507119</v>
+        <v>506701</v>
       </c>
       <c r="R13" t="n">
-        <v>7053255</v>
+        <v>7053096</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2222,17 +2231,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2253,12 +2258,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2276,10 +2281,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2292,30 +2297,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2323,13 +2324,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R14" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2363,7 +2364,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2378,32 +2379,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2421,10 +2417,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779255</v>
+        <v>122779298</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2437,40 +2433,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506701</v>
+        <v>507119</v>
       </c>
       <c r="R15" t="n">
-        <v>7053096</v>
+        <v>7053255</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2502,13 +2503,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2517,11 +2522,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779318</v>
+        <v>122779254</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,28 +1452,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507101</v>
+        <v>506701</v>
       </c>
       <c r="R8" t="n">
-        <v>7053264</v>
+        <v>7053096</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1521,11 +1521,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1541,29 +1536,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,10 +1571,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779188</v>
+        <v>122779318</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,46 +1587,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506664</v>
+        <v>507101</v>
       </c>
       <c r="R9" t="n">
-        <v>7053016</v>
+        <v>7053264</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1673,7 +1658,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,6 +1667,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1692,27 +1678,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1730,10 +1716,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779255</v>
+        <v>122779188</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,37 +1732,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R10" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1811,13 +1806,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1828,7 +1827,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1843,12 +1842,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1866,7 +1865,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779215</v>
+        <v>122779331</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1909,13 +1908,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506627</v>
+        <v>507003</v>
       </c>
       <c r="R11" t="n">
-        <v>7053057</v>
+        <v>7053201</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1945,6 +1944,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,7 +1963,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1997,10 +2001,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779089</v>
+        <v>122779255</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2013,46 +2017,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506686</v>
+        <v>506701</v>
       </c>
       <c r="R12" t="n">
-        <v>7053093</v>
+        <v>7053096</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2087,17 +2082,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2099,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2123,12 +2114,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2146,10 +2137,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779254</v>
+        <v>122779298</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,44 +2153,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506701</v>
+        <v>507119</v>
       </c>
       <c r="R13" t="n">
-        <v>7053096</v>
+        <v>7053255</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2231,13 +2223,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2258,12 +2254,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2281,10 +2277,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779331</v>
+        <v>122779089</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2297,40 +2293,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507003</v>
+        <v>506686</v>
       </c>
       <c r="R14" t="n">
-        <v>7053201</v>
+        <v>7053093</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2364,7 +2369,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2373,13 +2378,17 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2394,12 +2403,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2417,10 +2426,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779298</v>
+        <v>122779215</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2433,45 +2442,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507119</v>
+        <v>506627</v>
       </c>
       <c r="R15" t="n">
-        <v>7053255</v>
+        <v>7053057</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2503,17 +2507,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779318</v>
+        <v>122779188</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,41 +1587,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507101</v>
+        <v>506664</v>
       </c>
       <c r="R9" t="n">
-        <v>7053264</v>
+        <v>7053016</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1658,7 +1663,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,7 +1672,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1678,27 +1682,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1716,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779188</v>
+        <v>122779298</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,16 +1736,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1757,24 +1761,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506664</v>
+        <v>507119</v>
       </c>
       <c r="R10" t="n">
-        <v>7053016</v>
+        <v>7053255</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1823,11 +1823,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1865,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779331</v>
+        <v>122779318</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1881,26 +1876,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1908,13 +1907,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507003</v>
+        <v>507101</v>
       </c>
       <c r="R11" t="n">
-        <v>7053201</v>
+        <v>7053264</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1948,7 +1947,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1963,27 +1962,32 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2001,7 +2005,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779255</v>
+        <v>122779331</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -2044,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506701</v>
+        <v>507003</v>
       </c>
       <c r="R12" t="n">
-        <v>7053096</v>
+        <v>7053201</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2080,6 +2084,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,12 +2103,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2137,10 +2141,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779298</v>
+        <v>122779255</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2153,45 +2157,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507119</v>
+        <v>506701</v>
       </c>
       <c r="R13" t="n">
-        <v>7053255</v>
+        <v>7053096</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2223,17 +2222,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2242,6 +2237,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779089</v>
+        <v>122779215</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2293,46 +2293,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506686</v>
+        <v>506627</v>
       </c>
       <c r="R14" t="n">
-        <v>7053093</v>
+        <v>7053057</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2367,17 +2358,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2386,11 +2373,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2403,12 +2385,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2426,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779215</v>
+        <v>122779089</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2442,37 +2424,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506627</v>
+        <v>506686</v>
       </c>
       <c r="R15" t="n">
-        <v>7053057</v>
+        <v>7053093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2507,13 +2498,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2522,6 +2517,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779254</v>
+        <v>122779298</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,44 +1452,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506701</v>
+        <v>507119</v>
       </c>
       <c r="R8" t="n">
-        <v>7053096</v>
+        <v>7053255</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1521,13 +1522,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1548,12 +1553,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1571,7 +1576,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779188</v>
+        <v>122779089</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1623,10 +1628,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506664</v>
+        <v>506686</v>
       </c>
       <c r="R9" t="n">
-        <v>7053016</v>
+        <v>7053093</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1663,7 +1668,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779298</v>
+        <v>122779215</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,45 +1741,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507119</v>
+        <v>506627</v>
       </c>
       <c r="R10" t="n">
-        <v>7053255</v>
+        <v>7053057</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1806,17 +1806,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1837,12 +1833,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,30 +1872,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1907,13 +1899,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R11" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1947,7 +1939,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,32 +1954,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2005,7 +1992,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779331</v>
+        <v>122779255</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -2048,13 +2035,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507003</v>
+        <v>506701</v>
       </c>
       <c r="R12" t="n">
-        <v>7053201</v>
+        <v>7053096</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2084,11 +2071,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,7 +2085,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2141,10 +2128,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779255</v>
+        <v>122779318</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2157,26 +2144,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2184,10 +2175,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506701</v>
+        <v>507101</v>
       </c>
       <c r="R13" t="n">
-        <v>7053096</v>
+        <v>7053264</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2222,6 +2213,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2244,22 +2240,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2277,10 +2273,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779215</v>
+        <v>122779254</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2293,26 +2289,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R14" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779089</v>
+        <v>122779188</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506686</v>
+        <v>506664</v>
       </c>
       <c r="R15" t="n">
-        <v>7053093</v>
+        <v>7053016</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2273,10 +2273,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779254</v>
+        <v>122779188</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2289,41 +2289,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R14" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2358,13 +2363,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2373,6 +2382,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2385,12 +2399,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2408,10 +2422,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2424,46 +2438,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R15" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2498,17 +2507,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2517,11 +2522,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2273,10 +2273,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779188</v>
+        <v>122779254</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2289,46 +2289,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506664</v>
+        <v>506701</v>
       </c>
       <c r="R14" t="n">
-        <v>7053016</v>
+        <v>7053096</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2363,17 +2358,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2382,11 +2373,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2399,12 +2385,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2422,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779254</v>
+        <v>122779188</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2438,41 +2424,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506701</v>
+        <v>506664</v>
       </c>
       <c r="R15" t="n">
-        <v>7053096</v>
+        <v>7053016</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2507,13 +2498,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2522,6 +2517,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1439,7 +1439,7 @@
         <v>122779298</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>122779089</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>122779215</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779331</v>
+        <v>122779255</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1899,13 +1899,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507003</v>
+        <v>506701</v>
       </c>
       <c r="R11" t="n">
-        <v>7053201</v>
+        <v>7053096</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1935,11 +1935,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,7 +1949,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779255</v>
+        <v>122779331</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506701</v>
+        <v>507003</v>
       </c>
       <c r="R12" t="n">
-        <v>7053096</v>
+        <v>7053201</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2071,6 +2071,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2085,12 +2090,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2128,10 +2128,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779318</v>
+        <v>122779254</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>90973</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2144,28 +2144,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507101</v>
+        <v>506701</v>
       </c>
       <c r="R13" t="n">
-        <v>7053264</v>
+        <v>7053096</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2213,11 +2213,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2233,29 +2228,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2276,7 +2266,7 @@
         <v>122779188</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2422,10 +2412,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779254</v>
+        <v>122779318</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2438,28 +2428,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506701</v>
+        <v>507101</v>
       </c>
       <c r="R15" t="n">
-        <v>7053096</v>
+        <v>7053264</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2507,6 +2497,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2522,24 +2517,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2560,7 +2560,7 @@
         <v>122768066</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779298</v>
+        <v>122779089</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1477,20 +1477,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507119</v>
+        <v>506686</v>
       </c>
       <c r="R8" t="n">
-        <v>7053255</v>
+        <v>7053093</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,7 +1528,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,6 +1543,11 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1576,10 +1585,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779089</v>
+        <v>122779298</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1592,16 +1601,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,24 +1626,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506686</v>
+        <v>507119</v>
       </c>
       <c r="R9" t="n">
-        <v>7053093</v>
+        <v>7053255</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,11 +1688,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779215</v>
+        <v>122779255</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R10" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1819,6 +1819,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1856,10 +1861,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779255</v>
+        <v>122779254</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,26 +1877,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1952,11 +1961,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1969,12 +1973,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1995,7 +1999,7 @@
         <v>122779331</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2128,10 +2132,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779254</v>
+        <v>122779318</v>
       </c>
       <c r="B13" t="n">
-        <v>90973</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2144,28 +2148,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2175,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506701</v>
+        <v>507101</v>
       </c>
       <c r="R13" t="n">
-        <v>7053096</v>
+        <v>7053264</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2213,6 +2217,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2228,24 +2237,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2263,10 +2277,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779188</v>
+        <v>122779215</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2279,46 +2293,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506664</v>
+        <v>506627</v>
       </c>
       <c r="R14" t="n">
-        <v>7053016</v>
+        <v>7053057</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2353,17 +2358,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2372,11 +2373,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2389,12 +2385,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2412,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779318</v>
+        <v>122779188</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2428,41 +2424,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507101</v>
+        <v>506664</v>
       </c>
       <c r="R15" t="n">
-        <v>7053264</v>
+        <v>7053016</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2499,7 +2500,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2508,7 +2509,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2519,27 +2519,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779089</v>
+        <v>122779318</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,46 +1452,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506686</v>
+        <v>507101</v>
       </c>
       <c r="R8" t="n">
-        <v>7053093</v>
+        <v>7053264</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1528,7 +1523,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,6 +1532,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1547,27 +1543,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1585,10 +1581,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779298</v>
+        <v>122779215</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1601,45 +1597,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507119</v>
+        <v>506627</v>
       </c>
       <c r="R9" t="n">
-        <v>7053255</v>
+        <v>7053057</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1671,17 +1662,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1702,12 +1689,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1725,10 +1712,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779255</v>
+        <v>122779254</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1741,26 +1728,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1821,11 +1812,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1838,12 +1824,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1861,10 +1847,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779254</v>
+        <v>122779255</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,30 +1863,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1961,6 +1943,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1973,12 +1960,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1996,10 +1983,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122779331</v>
+        <v>122779188</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2012,40 +1999,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507003</v>
+        <v>506664</v>
       </c>
       <c r="R12" t="n">
-        <v>7053201</v>
+        <v>7053016</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2079,7 +2075,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,13 +2084,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2148,30 +2148,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2179,13 +2175,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R13" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2219,7 +2215,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2234,32 +2230,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2277,10 +2268,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779215</v>
+        <v>122779298</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2293,40 +2284,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506627</v>
+        <v>507119</v>
       </c>
       <c r="R14" t="n">
-        <v>7053057</v>
+        <v>7053255</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2358,13 +2354,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779188</v>
+        <v>122779089</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506664</v>
+        <v>506686</v>
       </c>
       <c r="R15" t="n">
-        <v>7053016</v>
+        <v>7053093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på en relativt grov gran. I skogsbeståndet kring fyndplatsen finns höga till mycket höga livsmiljövärden för tretåig hackspett baserat på volymen stående död (gran)ved.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B8" t="n">
-        <v>79853</v>
+        <v>78775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,30 +1452,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1483,13 +1479,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R8" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1523,7 +1519,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,32 +1534,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122779215</v>
+        <v>122779254</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>90984</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,26 +1588,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1624,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506627</v>
+        <v>506701</v>
       </c>
       <c r="R9" t="n">
-        <v>7053057</v>
+        <v>7053096</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1689,12 +1684,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122779254</v>
+        <v>122779255</v>
       </c>
       <c r="B10" t="n">
-        <v>90981</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1728,30 +1723,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1812,6 +1803,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1824,12 +1820,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1847,10 +1843,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122779255</v>
+        <v>122779318</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>79856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,26 +1859,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506701</v>
+        <v>507101</v>
       </c>
       <c r="R11" t="n">
-        <v>7053096</v>
+        <v>7053264</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1928,6 +1928,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1950,22 +1955,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2132,10 +2137,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122779331</v>
+        <v>122779215</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2175,13 +2180,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507003</v>
+        <v>506627</v>
       </c>
       <c r="R13" t="n">
-        <v>7053201</v>
+        <v>7053057</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2211,11 +2216,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122779298</v>
+        <v>122779089</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2309,20 +2309,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507119</v>
+        <v>506686</v>
       </c>
       <c r="R14" t="n">
-        <v>7053255</v>
+        <v>7053093</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2356,7 +2360,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2371,6 +2375,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2408,10 +2417,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122779089</v>
+        <v>122779298</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2424,16 +2433,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2449,24 +2458,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506686</v>
+        <v>507119</v>
       </c>
       <c r="R15" t="n">
-        <v>7053093</v>
+        <v>7053255</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2500,7 +2505,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på en gran.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2515,11 +2520,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med stora mängder död ved.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2560,7 +2560,7 @@
         <v>122768066</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>123590902</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>123590101</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>123589530</v>
       </c>
       <c r="B19" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>123591099</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>123589076</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123590902</v>
+        <v>123589530</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>97350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2706,36 +2706,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2744,13 +2739,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506945</v>
+        <v>507044</v>
       </c>
       <c r="R17" t="n">
-        <v>7053117</v>
+        <v>7053131</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2782,11 +2777,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2799,26 +2789,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2836,10 +2806,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123590101</v>
+        <v>123591099</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2852,47 +2822,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507030</v>
+        <v>506907</v>
       </c>
       <c r="R18" t="n">
-        <v>7053146</v>
+        <v>7053220</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2924,11 +2884,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2955,12 +2910,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2978,10 +2933,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123589530</v>
+        <v>123589076</v>
       </c>
       <c r="B19" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2990,46 +2945,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507044</v>
+        <v>507050</v>
       </c>
       <c r="R19" t="n">
-        <v>7053131</v>
+        <v>7053220</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3073,6 +3023,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3090,10 +3060,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123591099</v>
+        <v>123771494</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3106,37 +3076,49 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506907</v>
+        <v>506638</v>
       </c>
       <c r="R20" t="n">
-        <v>7053220</v>
+        <v>7053070</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3160,12 +3142,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3182,6 +3169,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3194,12 +3186,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3217,10 +3209,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123589076</v>
+        <v>123590101</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3233,37 +3225,47 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507050</v>
+        <v>507030</v>
       </c>
       <c r="R21" t="n">
-        <v>7053220</v>
+        <v>7053146</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3295,6 +3297,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3321,12 +3328,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3341,6 +3348,148 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123590902</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57487</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506945</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7053117</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2560,7 +2560,7 @@
         <v>122768066</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123589530</v>
+        <v>123589076</v>
       </c>
       <c r="B17" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2706,46 +2706,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507044</v>
+        <v>507050</v>
       </c>
       <c r="R17" t="n">
-        <v>7053131</v>
+        <v>7053220</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2789,6 +2784,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2806,10 +2821,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123591099</v>
+        <v>123589530</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,41 +2833,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506907</v>
+        <v>507044</v>
       </c>
       <c r="R18" t="n">
-        <v>7053220</v>
+        <v>7053131</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2896,26 +2916,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123589076</v>
+        <v>123591099</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507050</v>
+        <v>506907</v>
       </c>
       <c r="R19" t="n">
         <v>7053220</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771494</v>
+        <v>123590101</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3094,11 +3094,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3108,17 +3106,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506638</v>
+        <v>507030</v>
       </c>
       <c r="R20" t="n">
-        <v>7053070</v>
+        <v>7053146</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3142,17 +3140,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3169,11 +3167,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3186,12 +3179,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3209,10 +3202,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123590101</v>
+        <v>123590902</v>
       </c>
       <c r="B21" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3259,10 +3252,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507030</v>
+        <v>506945</v>
       </c>
       <c r="R21" t="n">
-        <v>7053146</v>
+        <v>7053117</v>
       </c>
       <c r="S21" t="n">
         <v>7</v>
@@ -3299,7 +3292,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3351,10 +3344,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123590902</v>
+        <v>123771494</v>
       </c>
       <c r="B22" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3385,9 +3378,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3397,17 +3392,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506945</v>
+        <v>506638</v>
       </c>
       <c r="R22" t="n">
-        <v>7053117</v>
+        <v>7053070</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3431,17 +3426,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3458,6 +3453,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2560,7 +2560,7 @@
         <v>122768066</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123589076</v>
+        <v>123591099</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507050</v>
+        <v>506907</v>
       </c>
       <c r="R17" t="n">
         <v>7053220</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>123589530</v>
       </c>
       <c r="B18" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123591099</v>
+        <v>123589076</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506907</v>
+        <v>507050</v>
       </c>
       <c r="R19" t="n">
         <v>7053220</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>123590101</v>
       </c>
       <c r="B20" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123590902</v>
+        <v>123771494</v>
       </c>
       <c r="B21" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3236,9 +3236,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3248,17 +3250,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506945</v>
+        <v>506638</v>
       </c>
       <c r="R21" t="n">
-        <v>7053117</v>
+        <v>7053070</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3282,17 +3284,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3309,6 +3311,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3321,12 +3328,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3344,10 +3351,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771494</v>
+        <v>123590902</v>
       </c>
       <c r="B22" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3378,11 +3385,9 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3392,17 +3397,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506638</v>
+        <v>506945</v>
       </c>
       <c r="R22" t="n">
-        <v>7053070</v>
+        <v>7053117</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3426,17 +3431,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3453,11 +3458,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123591099</v>
+        <v>123589076</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506907</v>
+        <v>507050</v>
       </c>
       <c r="R17" t="n">
         <v>7053220</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>123589530</v>
       </c>
       <c r="B18" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123589076</v>
+        <v>123591099</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507050</v>
+        <v>506907</v>
       </c>
       <c r="R19" t="n">
         <v>7053220</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123590101</v>
+        <v>123590902</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507030</v>
+        <v>506945</v>
       </c>
       <c r="R20" t="n">
-        <v>7053146</v>
+        <v>7053117</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3202,7 +3202,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771494</v>
+        <v>123590101</v>
       </c>
       <c r="B21" t="n">
         <v>57491</v>
@@ -3236,11 +3236,9 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3250,17 +3248,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506638</v>
+        <v>507030</v>
       </c>
       <c r="R21" t="n">
-        <v>7053070</v>
+        <v>7053146</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3284,17 +3282,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,11 +3309,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3328,12 +3321,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3351,7 +3344,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123590902</v>
+        <v>123771494</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -3385,9 +3378,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3397,17 +3392,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506945</v>
+        <v>506638</v>
       </c>
       <c r="R22" t="n">
-        <v>7053117</v>
+        <v>7053070</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3431,17 +3426,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3458,6 +3453,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123589076</v>
+        <v>123591099</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507050</v>
+        <v>506907</v>
       </c>
       <c r="R17" t="n">
         <v>7053220</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123591099</v>
+        <v>123589076</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506907</v>
+        <v>507050</v>
       </c>
       <c r="R19" t="n">
         <v>7053220</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123590902</v>
+        <v>123771494</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -3094,9 +3094,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3106,17 +3108,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506945</v>
+        <v>506638</v>
       </c>
       <c r="R20" t="n">
-        <v>7053117</v>
+        <v>7053070</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3140,17 +3142,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3167,6 +3169,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3179,12 +3186,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3344,7 +3351,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771494</v>
+        <v>123590902</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -3378,11 +3385,9 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3392,17 +3397,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506638</v>
+        <v>506945</v>
       </c>
       <c r="R22" t="n">
-        <v>7053070</v>
+        <v>7053117</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3426,17 +3431,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3453,11 +3458,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -3060,7 +3060,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771494</v>
+        <v>123590101</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -3094,11 +3094,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3108,17 +3106,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506638</v>
+        <v>507030</v>
       </c>
       <c r="R20" t="n">
-        <v>7053070</v>
+        <v>7053146</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3142,17 +3140,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3169,11 +3167,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3186,12 +3179,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3209,7 +3202,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123590101</v>
+        <v>123771494</v>
       </c>
       <c r="B21" t="n">
         <v>57491</v>
@@ -3243,9 +3236,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3255,17 +3250,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507030</v>
+        <v>506638</v>
       </c>
       <c r="R21" t="n">
-        <v>7053146</v>
+        <v>7053070</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3289,17 +3284,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3316,6 +3311,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2821,10 +2821,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123589530</v>
+        <v>123589076</v>
       </c>
       <c r="B18" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2833,46 +2833,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507044</v>
+        <v>507050</v>
       </c>
       <c r="R18" t="n">
-        <v>7053131</v>
+        <v>7053220</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2916,6 +2911,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2933,10 +2948,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123589076</v>
+        <v>123589530</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2945,41 +2960,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507050</v>
+        <v>507044</v>
       </c>
       <c r="R19" t="n">
-        <v>7053220</v>
+        <v>7053131</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3023,26 +3043,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771494</v>
+        <v>123590902</v>
       </c>
       <c r="B21" t="n">
         <v>57491</v>
@@ -3236,11 +3236,9 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3250,17 +3248,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506638</v>
+        <v>506945</v>
       </c>
       <c r="R21" t="n">
-        <v>7053070</v>
+        <v>7053117</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3284,17 +3282,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,11 +3309,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3328,12 +3321,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3351,7 +3344,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123590902</v>
+        <v>123771494</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -3385,9 +3378,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3397,17 +3392,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506945</v>
+        <v>506638</v>
       </c>
       <c r="R22" t="n">
-        <v>7053117</v>
+        <v>7053070</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3431,17 +3426,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3458,6 +3453,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 69641-2020 artfynd.xlsx
+++ b/artfynd/A 69641-2020 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123591099</v>
+        <v>123589530</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2706,41 +2706,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506907</v>
+        <v>507044</v>
       </c>
       <c r="R17" t="n">
-        <v>7053220</v>
+        <v>7053131</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2784,26 +2789,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2948,10 +2933,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123589530</v>
+        <v>123591099</v>
       </c>
       <c r="B19" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2960,46 +2945,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507044</v>
+        <v>506907</v>
       </c>
       <c r="R19" t="n">
-        <v>7053131</v>
+        <v>7053220</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3043,6 +3023,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123590902</v>
+        <v>123771494</v>
       </c>
       <c r="B21" t="n">
         <v>57491</v>
@@ -3236,9 +3236,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3248,17 +3250,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506945</v>
+        <v>506638</v>
       </c>
       <c r="R21" t="n">
-        <v>7053117</v>
+        <v>7053070</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3282,17 +3284,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3309,6 +3311,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3321,12 +3328,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3344,7 +3351,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771494</v>
+        <v>123590902</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -3378,11 +3385,9 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3392,17 +3397,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506638</v>
+        <v>506945</v>
       </c>
       <c r="R22" t="n">
-        <v>7053070</v>
+        <v>7053117</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3426,17 +3431,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bohål i en vedsvampsangripen granhögstubbe på ca 3 meters höjd som möjligen är skapat av tretåig hackspett.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3453,11 +3458,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog med gott om särskilt stående död ved.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
